--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.795550549015184</v>
+        <v>1.266776964214967</v>
       </c>
       <c r="D2" t="n">
-        <v>27.51156957497125</v>
+        <v>4.470630055932828</v>
       </c>
       <c r="E2" t="n">
-        <v>11.85422070361245</v>
+        <v>1.926310864337023</v>
       </c>
       <c r="F2" t="n">
-        <v>9.53951451389268</v>
+        <v>1.550171108507561</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.29763711554987</v>
+        <v>5.735866031276854</v>
       </c>
       <c r="D3" t="n">
-        <v>20.78995483935024</v>
+        <v>3.378367661394414</v>
       </c>
       <c r="E3" t="n">
-        <v>11.85422070361245</v>
+        <v>1.926310864337023</v>
       </c>
       <c r="F3" t="n">
-        <v>9.53951451389268</v>
+        <v>1.550171108507561</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.48135742617468</v>
+        <v>5.278220581753386</v>
       </c>
       <c r="D4" t="n">
-        <v>12.83766160776781</v>
+        <v>2.086120011262269</v>
       </c>
       <c r="E4" t="n">
-        <v>11.85422070361245</v>
+        <v>1.926310864337023</v>
       </c>
       <c r="F4" t="n">
-        <v>9.53951451389268</v>
+        <v>1.550171108507561</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.83209074222392</v>
+        <v>3.060214745611388</v>
       </c>
       <c r="D5" t="n">
-        <v>18.50354274468294</v>
+        <v>3.006825696010977</v>
       </c>
       <c r="E5" t="n">
-        <v>11.85422070361245</v>
+        <v>1.926310864337023</v>
       </c>
       <c r="F5" t="n">
-        <v>9.53951451389268</v>
+        <v>1.550171108507561</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.17610609002049</v>
+        <v>3.441117239628329</v>
       </c>
       <c r="D6" t="n">
-        <v>31.42009265139462</v>
+        <v>5.105765055851625</v>
       </c>
       <c r="E6" t="n">
-        <v>11.85422070361245</v>
+        <v>1.926310864337023</v>
       </c>
       <c r="F6" t="n">
-        <v>9.53951451389268</v>
+        <v>1.550171108507561</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.10827451782391</v>
+        <v>3.917594609146386</v>
       </c>
       <c r="D7" t="n">
-        <v>12.30401921686116</v>
+        <v>1.999403122739939</v>
       </c>
       <c r="E7" t="n">
-        <v>11.85422070361245</v>
+        <v>1.926310864337023</v>
       </c>
       <c r="F7" t="n">
-        <v>9.53951451389268</v>
+        <v>1.550171108507561</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>4.154522979477824</v>
+        <v>0.6751099841651464</v>
       </c>
       <c r="D8" t="n">
-        <v>7.750683491291947</v>
+        <v>1.259486067334942</v>
       </c>
       <c r="E8" t="n">
-        <v>11.85422070361245</v>
+        <v>1.926310864337023</v>
       </c>
       <c r="F8" t="n">
-        <v>9.53951451389268</v>
+        <v>1.550171108507561</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>2.781315244734933</v>
+        <v>0.4519637272694266</v>
       </c>
       <c r="D9" t="n">
-        <v>16.79261609789223</v>
+        <v>2.728800115907488</v>
       </c>
       <c r="E9" t="n">
-        <v>11.85422070361245</v>
+        <v>1.926310864337023</v>
       </c>
       <c r="F9" t="n">
-        <v>9.53951451389268</v>
+        <v>1.550171108507561</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>22.55695808447343</v>
+        <v>3.665505688726932</v>
       </c>
       <c r="D10" t="n">
-        <v>26.87071696102914</v>
+        <v>4.366491506167235</v>
       </c>
       <c r="E10" t="n">
-        <v>11.85422070361245</v>
+        <v>1.926310864337023</v>
       </c>
       <c r="F10" t="n">
-        <v>9.53951451389268</v>
+        <v>1.550171108507561</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>13.93444393505452</v>
+        <v>2.26434713944636</v>
       </c>
       <c r="D11" t="n">
-        <v>5.722472186428277</v>
+        <v>0.929901730294595</v>
       </c>
       <c r="E11" t="n">
-        <v>11.85422070361245</v>
+        <v>1.926310864337023</v>
       </c>
       <c r="F11" t="n">
-        <v>9.53951451389268</v>
+        <v>1.550171108507561</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>20.4256027307294</v>
+        <v>3.319160443743527</v>
       </c>
       <c r="D12" t="n">
-        <v>15.04952376922516</v>
+        <v>2.445547612499089</v>
       </c>
       <c r="E12" t="n">
-        <v>11.85422070361245</v>
+        <v>1.926310864337023</v>
       </c>
       <c r="F12" t="n">
-        <v>9.53951451389268</v>
+        <v>1.550171108507561</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.54227818416029</v>
+        <v>4.150620204926047</v>
       </c>
       <c r="D13" t="n">
-        <v>9.404770286509496</v>
+        <v>1.528275171557793</v>
       </c>
       <c r="E13" t="n">
-        <v>11.85422070361245</v>
+        <v>1.926310864337023</v>
       </c>
       <c r="F13" t="n">
-        <v>9.53951451389268</v>
+        <v>1.550171108507561</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>37.77389248894794</v>
+        <v>6.138257529454041</v>
       </c>
       <c r="D14" t="n">
-        <v>20.84437971445717</v>
+        <v>3.387211703599291</v>
       </c>
       <c r="E14" t="n">
-        <v>11.85422070361245</v>
+        <v>1.926310864337023</v>
       </c>
       <c r="F14" t="n">
-        <v>9.53951451389268</v>
+        <v>1.550171108507561</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>24.06862686119882</v>
+        <v>3.911151864944808</v>
       </c>
       <c r="D15" t="n">
-        <v>20.52153382755868</v>
+        <v>3.334749246978286</v>
       </c>
       <c r="E15" t="n">
-        <v>11.85422070361245</v>
+        <v>1.926310864337023</v>
       </c>
       <c r="F15" t="n">
-        <v>9.53951451389268</v>
+        <v>1.550171108507561</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>6.397708906850466</v>
+        <v>1.039627697363201</v>
       </c>
       <c r="D16" t="n">
-        <v>7.37058352004049</v>
+        <v>1.19771982200658</v>
       </c>
       <c r="E16" t="n">
-        <v>11.85422070361245</v>
+        <v>1.926310864337023</v>
       </c>
       <c r="F16" t="n">
-        <v>9.53951451389268</v>
+        <v>1.550171108507561</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>8.378289548992589</v>
+        <v>1.361472051711296</v>
       </c>
       <c r="D17" t="n">
-        <v>6.876459643232231</v>
+        <v>1.117424692025238</v>
       </c>
       <c r="E17" t="n">
-        <v>11.85422070361245</v>
+        <v>1.926310864337023</v>
       </c>
       <c r="F17" t="n">
-        <v>9.53951451389268</v>
+        <v>1.550171108507561</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>41.10637289257636</v>
+        <v>6.679785595043659</v>
       </c>
       <c r="D18" t="n">
-        <v>32.61794710543233</v>
+        <v>5.300416404632753</v>
       </c>
       <c r="E18" t="n">
-        <v>11.85422070361245</v>
+        <v>1.926310864337023</v>
       </c>
       <c r="F18" t="n">
-        <v>9.53951451389268</v>
+        <v>1.550171108507561</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>43.64603031668536</v>
+        <v>7.092479926461372</v>
       </c>
       <c r="D19" t="n">
-        <v>41.52139962981662</v>
+        <v>6.747227439845201</v>
       </c>
       <c r="E19" t="n">
-        <v>11.85422070361245</v>
+        <v>1.926310864337023</v>
       </c>
       <c r="F19" t="n">
-        <v>9.53951451389268</v>
+        <v>1.550171108507561</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>16.86741581371875</v>
+        <v>2.740955069729297</v>
       </c>
       <c r="D20" t="n">
-        <v>19.73446822782769</v>
+        <v>3.206851087021999</v>
       </c>
       <c r="E20" t="n">
-        <v>11.85422070361245</v>
+        <v>1.926310864337023</v>
       </c>
       <c r="F20" t="n">
-        <v>9.53951451389268</v>
+        <v>1.550171108507561</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>19.78255208620732</v>
+        <v>3.21466471400869</v>
       </c>
       <c r="D21" t="n">
-        <v>25.9722236343473</v>
+        <v>4.220486340581437</v>
       </c>
       <c r="E21" t="n">
-        <v>11.85422070361245</v>
+        <v>1.926310864337023</v>
       </c>
       <c r="F21" t="n">
-        <v>9.53951451389268</v>
+        <v>1.550171108507561</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
